--- a/artfynd/A 14312-2025 artfynd.xlsx
+++ b/artfynd/A 14312-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,6 +819,128 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124657295</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bornsberg, Bornsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>502769</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6602817</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14312-2025 artfynd.xlsx
+++ b/artfynd/A 14312-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124658049</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>124657295</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 14312-2025 artfynd.xlsx
+++ b/artfynd/A 14312-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124658049</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>124657295</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14312-2025 artfynd.xlsx
+++ b/artfynd/A 14312-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124658049</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>124657295</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14312-2025 artfynd.xlsx
+++ b/artfynd/A 14312-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658049</v>
+        <v>124657295</v>
       </c>
       <c r="B2" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502741</v>
+        <v>502769</v>
       </c>
       <c r="R2" t="n">
-        <v>6602836</v>
+        <v>6602817</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,24 +748,9 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hack i död tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,11 +762,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>tall</t>
@@ -792,39 +772,34 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124657295</v>
+        <v>124658049</v>
       </c>
       <c r="B3" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -857,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502769</v>
+        <v>502741</v>
       </c>
       <c r="R3" t="n">
-        <v>6602817</v>
+        <v>6602836</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,9 +865,24 @@
           <t>2025-05-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +894,11 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>tall</t>
@@ -914,23 +909,150 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124658631</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bornsberg, Bornsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>502682</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6602833</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Dead wood</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mattias Drejby</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Mattias Drejby</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14312-2025 artfynd.xlsx
+++ b/artfynd/A 14312-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124657295</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -931,6 +941,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124658049</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1053,8 +1068,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124658631</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>